--- a/src/templates/report.xlsx
+++ b/src/templates/report.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luke\Computer Science\repos\cpf-concours\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047432B6-2BE3-43B8-8777-B1744AAB604F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275F41F8-05DF-43F7-8C5F-D60CB4C79C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="judges" sheetId="1" r:id="rId1"/>
-    <sheet name="contestants" sheetId="2" r:id="rId2"/>
-    <sheet name="sformats" sheetId="3" r:id="rId3"/>
-    <sheet name="grades" sheetId="4" r:id="rId4"/>
-    <sheet name="levels" sheetId="5" r:id="rId5"/>
-    <sheet name="durations" sheetId="6" r:id="rId6"/>
-    <sheet name="categories" sheetId="7" r:id="rId7"/>
-    <sheet name="places" sheetId="8" r:id="rId8"/>
-    <sheet name="schools_given" sheetId="9" r:id="rId9"/>
-    <sheet name="schools_received" sheetId="10" r:id="rId10"/>
+    <sheet name="judges_adjust" sheetId="11" r:id="rId2"/>
+    <sheet name="contestants" sheetId="2" r:id="rId3"/>
+    <sheet name="sformats" sheetId="3" r:id="rId4"/>
+    <sheet name="grades" sheetId="4" r:id="rId5"/>
+    <sheet name="levels" sheetId="5" r:id="rId6"/>
+    <sheet name="durations" sheetId="6" r:id="rId7"/>
+    <sheet name="categories" sheetId="7" r:id="rId8"/>
+    <sheet name="places" sheetId="8" r:id="rId9"/>
+    <sheet name="schools_given" sheetId="9" r:id="rId10"/>
+    <sheet name="schools_received" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
   <si>
     <t>Judge</t>
   </si>
@@ -522,6 +523,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D290C4-6DF1-4A0C-8780-F129CDE8CAE1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F318666E-D9D6-456F-B813-C218F0802663}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -531,6 +541,72 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DC6DDC-7802-42F3-AB68-46EF7C297000}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E29161B-47C6-4DDA-829C-7363C4EC367F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -539,7 +615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74877F44-2510-4345-BDB6-89A642DC99DF}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -548,7 +624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62BBA31-CA6C-45C8-A22F-2D7E644E656B}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -557,7 +633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7536A744-182D-4BED-8101-5E90E5335BB3}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -566,7 +642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA37E19E-71B0-4981-A27A-65F4CF49650F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -575,7 +651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE95C41-1A9D-446B-922D-755D62D95E84}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -584,20 +660,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F715B5-CDA7-4378-A61A-53470693CA9F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D290C4-6DF1-4A0C-8780-F129CDE8CAE1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/templates/report.xlsx
+++ b/src/templates/report.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luke\Computer Science\repos\cpf-concours\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275F41F8-05DF-43F7-8C5F-D60CB4C79C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3CC6CD-2025-48EF-AB24-C89CD071FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="judges" sheetId="1" r:id="rId1"/>
     <sheet name="judges_adjust" sheetId="11" r:id="rId2"/>
-    <sheet name="contestants" sheetId="2" r:id="rId3"/>
-    <sheet name="sformats" sheetId="3" r:id="rId4"/>
-    <sheet name="grades" sheetId="4" r:id="rId5"/>
-    <sheet name="levels" sheetId="5" r:id="rId6"/>
-    <sheet name="durations" sheetId="6" r:id="rId7"/>
-    <sheet name="categories" sheetId="7" r:id="rId8"/>
-    <sheet name="places" sheetId="8" r:id="rId9"/>
-    <sheet name="schools_given" sheetId="9" r:id="rId10"/>
-    <sheet name="schools_received" sheetId="10" r:id="rId11"/>
+    <sheet name="contestants" sheetId="14" r:id="rId3"/>
+    <sheet name="contestants_adjust" sheetId="13" r:id="rId4"/>
+    <sheet name="sformats" sheetId="3" r:id="rId5"/>
+    <sheet name="grades" sheetId="4" r:id="rId6"/>
+    <sheet name="levels" sheetId="5" r:id="rId7"/>
+    <sheet name="durations" sheetId="6" r:id="rId8"/>
+    <sheet name="categories" sheetId="7" r:id="rId9"/>
+    <sheet name="places" sheetId="8" r:id="rId10"/>
+    <sheet name="schools_given" sheetId="9" r:id="rId11"/>
+    <sheet name="schools_received" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="18">
   <si>
     <t>Judge</t>
   </si>
@@ -86,6 +87,9 @@
   </si>
   <si>
     <t>N I</t>
+  </si>
+  <si>
+    <t>Contestant</t>
   </si>
 </sst>
 </file>
@@ -523,6 +527,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F715B5-CDA7-4378-A61A-53470693CA9F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D290C4-6DF1-4A0C-8780-F129CDE8CAE1}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -531,7 +544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F318666E-D9D6-456F-B813-C218F0802663}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -607,15 +620,120 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E29161B-47C6-4DDA-829C-7363C4EC367F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65682D91-7DEE-4B54-9303-16CB1458FB93}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B710EA0-CA51-41B1-85DB-33B94040101F}">
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74877F44-2510-4345-BDB6-89A642DC99DF}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -624,7 +742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62BBA31-CA6C-45C8-A22F-2D7E644E656B}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -633,7 +751,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7536A744-182D-4BED-8101-5E90E5335BB3}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -642,7 +760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA37E19E-71B0-4981-A27A-65F4CF49650F}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -651,20 +769,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE95C41-1A9D-446B-922D-755D62D95E84}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F715B5-CDA7-4378-A61A-53470693CA9F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/templates/report.xlsx
+++ b/src/templates/report.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luke\Computer Science\repos\cpf-concours\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3CC6CD-2025-48EF-AB24-C89CD071FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AB67A4-D7F0-4E1E-948A-AF59C3B486AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="judges" sheetId="1" r:id="rId1"/>
-    <sheet name="judges_adjust" sheetId="11" r:id="rId2"/>
-    <sheet name="contestants" sheetId="14" r:id="rId3"/>
-    <sheet name="contestants_adjust" sheetId="13" r:id="rId4"/>
-    <sheet name="sformats" sheetId="3" r:id="rId5"/>
-    <sheet name="grades" sheetId="4" r:id="rId6"/>
-    <sheet name="levels" sheetId="5" r:id="rId7"/>
-    <sheet name="durations" sheetId="6" r:id="rId8"/>
-    <sheet name="categories" sheetId="7" r:id="rId9"/>
-    <sheet name="places" sheetId="8" r:id="rId10"/>
-    <sheet name="schools_given" sheetId="9" r:id="rId11"/>
-    <sheet name="schools_received" sheetId="10" r:id="rId12"/>
+    <sheet name="contestants" sheetId="23" r:id="rId1"/>
+    <sheet name="contestants_adjust" sheetId="24" r:id="rId2"/>
+    <sheet name="judges" sheetId="1" r:id="rId3"/>
+    <sheet name="judges_adjust" sheetId="11" r:id="rId4"/>
+    <sheet name="categories" sheetId="16" r:id="rId5"/>
+    <sheet name="formats" sheetId="17" r:id="rId6"/>
+    <sheet name="grades" sheetId="22" r:id="rId7"/>
+    <sheet name="levels" sheetId="21" r:id="rId8"/>
+    <sheet name="durations" sheetId="20" r:id="rId9"/>
+    <sheet name="durations_adjust" sheetId="25" r:id="rId10"/>
+    <sheet name="schools_given" sheetId="19" r:id="rId11"/>
+    <sheet name="schools_received" sheetId="18" r:id="rId12"/>
+    <sheet name="places" sheetId="8" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="24">
   <si>
     <t>Judge</t>
   </si>
@@ -90,6 +91,24 @@
   </si>
   <si>
     <t>Contestant</t>
+  </si>
+  <si>
+    <t>Format</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>School</t>
   </si>
 </sst>
 </file>
@@ -461,6 +480,345 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B1B1A6-77BA-4B5F-B57F-EA67873BD1AF}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E1ABD5-ADB2-4DF0-BFBA-D2844F79AC2C}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9428BBEB-AE09-4206-8D75-ED9A87413722}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F08DCBB-D175-4513-8600-35D4C74F475D}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F715B5-CDA7-4378-A61A-53470693CA9F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32A42C1E-E4A3-4B99-AFC7-B3AD19EE2004}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -526,34 +884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F715B5-CDA7-4378-A61A-53470693CA9F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D290C4-6DF1-4A0C-8780-F129CDE8CAE1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F318666E-D9D6-456F-B813-C218F0802663}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5DC6DDC-7802-42F3-AB68-46EF7C297000}">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -619,55 +950,64 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65682D91-7DEE-4B54-9303-16CB1458FB93}">
-  <dimension ref="A1:N1"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642F5BCE-91B4-45C9-BB46-FE30F61A23FE}">
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -676,55 +1016,64 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B710EA0-CA51-41B1-85DB-33B94040101F}">
-  <dimension ref="A1:N1"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38439C5D-7B17-4C5A-8E3A-1DEAF695CFA4}">
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -733,47 +1082,200 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74877F44-2510-4345-BDB6-89A642DC99DF}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{655E84FE-8528-42DB-81A6-BC97A0E9D785}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62BBA31-CA6C-45C8-A22F-2D7E644E656B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82842637-9C55-4613-9A3D-5E83244837E9}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7536A744-182D-4BED-8101-5E90E5335BB3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA37E19E-71B0-4981-A27A-65F4CF49650F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE95C41-1A9D-446B-922D-755D62D95E84}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653CBE1A-FE09-45DA-8160-361132CBEAED}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/templates/report.xlsx
+++ b/src/templates/report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luke\Computer Science\repos\cpf-concours\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63AB67A4-D7F0-4E1E-948A-AF59C3B486AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA65B354-367D-4B3E-8A79-70AB32DC8C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contestants" sheetId="23" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="34">
   <si>
     <t>Judge</t>
   </si>
@@ -109,6 +109,36 @@
   </si>
   <si>
     <t>School</t>
+  </si>
+  <si>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>2nd</t>
+  </si>
+  <si>
+    <t>3rd</t>
+  </si>
+  <si>
+    <t>4th</t>
+  </si>
+  <si>
+    <t>5th</t>
+  </si>
+  <si>
+    <t>6th</t>
+  </si>
+  <si>
+    <t>7th</t>
+  </si>
+  <si>
+    <t>8th</t>
+  </si>
+  <si>
+    <t>9th</t>
+  </si>
+  <si>
+    <t>10th</t>
   </si>
 </sst>
 </file>
@@ -139,7 +169,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,6 +206,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0066CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -189,13 +225,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -204,6 +243,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCCCFF"/>
+      <color rgb="FF0066CC"/>
       <color rgb="FF6600FF"/>
     </mruColors>
   </colors>
@@ -745,10 +786,51 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F715B5-CDA7-4378-A61A-53470693CA9F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.81640625" style="8" customWidth="1"/>
+    <col min="2" max="11" width="25.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/templates/report.xlsx
+++ b/src/templates/report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luke\Computer Science\repos\cpf-concours\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA65B354-367D-4B3E-8A79-70AB32DC8C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C94C3B0-5AF4-4538-9013-0113F00A4514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contestants" sheetId="23" r:id="rId1"/>
@@ -18,14 +18,15 @@
     <sheet name="judges" sheetId="1" r:id="rId3"/>
     <sheet name="judges_adjust" sheetId="11" r:id="rId4"/>
     <sheet name="categories" sheetId="16" r:id="rId5"/>
-    <sheet name="formats" sheetId="17" r:id="rId6"/>
-    <sheet name="grades" sheetId="22" r:id="rId7"/>
-    <sheet name="levels" sheetId="21" r:id="rId8"/>
-    <sheet name="durations" sheetId="20" r:id="rId9"/>
-    <sheet name="durations_adjust" sheetId="25" r:id="rId10"/>
-    <sheet name="schools_given" sheetId="19" r:id="rId11"/>
-    <sheet name="schools_received" sheetId="18" r:id="rId12"/>
-    <sheet name="places" sheetId="8" r:id="rId13"/>
+    <sheet name="category_variances" sheetId="26" r:id="rId6"/>
+    <sheet name="formats" sheetId="17" r:id="rId7"/>
+    <sheet name="grades" sheetId="22" r:id="rId8"/>
+    <sheet name="levels" sheetId="21" r:id="rId9"/>
+    <sheet name="durations" sheetId="20" r:id="rId10"/>
+    <sheet name="durations_adjust" sheetId="25" r:id="rId11"/>
+    <sheet name="schools_given" sheetId="19" r:id="rId12"/>
+    <sheet name="schools_received" sheetId="18" r:id="rId13"/>
+    <sheet name="places" sheetId="8" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="34">
   <si>
     <t>Judge</t>
   </si>
@@ -225,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -234,7 +235,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,6 +587,72 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653CBE1A-FE09-45DA-8160-361132CBEAED}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5E1ABD5-ADB2-4DF0-BFBA-D2844F79AC2C}">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -652,7 +718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9428BBEB-AE09-4206-8D75-ED9A87413722}">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -718,7 +784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F08DCBB-D175-4513-8600-35D4C74F475D}">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -784,12 +850,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80F715B5-CDA7-4378-A61A-53470693CA9F}">
   <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" customWidth="1"/>
     <col min="2" max="11" width="25.81640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1099,6 +1165,72 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CA00A54-28E9-497D-9F41-B6E51533DE81}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38439C5D-7B17-4C5A-8E3A-1DEAF695CFA4}">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1164,7 +1296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{655E84FE-8528-42DB-81A6-BC97A0E9D785}">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1230,7 +1362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82842637-9C55-4613-9A3D-5E83244837E9}">
   <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1294,70 +1426,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{653CBE1A-FE09-45DA-8160-361132CBEAED}">
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="22.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/templates/report.xlsx
+++ b/src/templates/report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luke\Computer Science\repos\cpf-concours\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C94C3B0-5AF4-4538-9013-0113F00A4514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6276B4-DD9F-40E7-88A1-91B3FECF1C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contestants" sheetId="23" r:id="rId1"/>
@@ -46,36 +46,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>I1</t>
-  </si>
-  <si>
-    <t>I2</t>
-  </si>
-  <si>
-    <t>I3</t>
-  </si>
-  <si>
-    <t>I4</t>
-  </si>
-  <si>
-    <t>I5</t>
-  </si>
-  <si>
     <t>Total T</t>
   </si>
   <si>
@@ -140,6 +110,36 @@
   </si>
   <si>
     <t>10th</t>
+  </si>
+  <si>
+    <t>Trad - expression orale</t>
+  </si>
+  <si>
+    <t>Trad - Cohérence</t>
+  </si>
+  <si>
+    <t>Trad - Langage</t>
+  </si>
+  <si>
+    <t>Trad - Mis en scène</t>
+  </si>
+  <si>
+    <t>Trad - Questions</t>
+  </si>
+  <si>
+    <t>Imp - Cohérence</t>
+  </si>
+  <si>
+    <t>Imp - Vocab</t>
+  </si>
+  <si>
+    <t>Imp - Aisance</t>
+  </si>
+  <si>
+    <t>Imp - Langue parlée</t>
+  </si>
+  <si>
+    <t>Imp - Questions</t>
   </si>
 </sst>
 </file>
@@ -530,55 +530,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -596,55 +596,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -662,55 +662,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -728,55 +728,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -794,55 +794,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -861,37 +861,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="H1" s="7" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -910,55 +910,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -979,52 +979,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1045,52 +1045,52 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1108,55 +1108,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1174,55 +1174,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1240,55 +1240,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1306,55 +1306,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1372,55 +1372,55 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="M1" s="4" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
